--- a/labs/lab-04-workbook-rules/data/Northstar_Work_Orders.xlsx
+++ b/labs/lab-04-workbook-rules/data/Northstar_Work_Orders.xlsx
@@ -13,15 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt_Log" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence_Log" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'About_This_Data'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Work_Orders'!$A$1:$M$121</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Technicians'!$A$1:$D$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Control'!$A$1:$B$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Prompt_Log'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Checks'!$A$1:$C$2</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -561,7 +555,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1331,7 +1324,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="F14" s="2"/>
       <c r="G14" s="4" t="n">
         <v>46278</v>
       </c>
@@ -1971,7 +1964,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="F26" s="2"/>
       <c r="G26" s="4" t="n">
         <v>46266</v>
       </c>
@@ -3259,7 +3252,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr"/>
+      <c r="F50" s="2"/>
       <c r="G50" s="4" t="n">
         <v>46242</v>
       </c>
@@ -4547,7 +4540,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr"/>
+      <c r="F74" s="2"/>
       <c r="G74" s="4" t="n">
         <v>46218</v>
       </c>
@@ -5187,7 +5180,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr"/>
+      <c r="F86" s="2"/>
       <c r="G86" s="4" t="n">
         <v>46286</v>
       </c>
@@ -6475,7 +6468,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr"/>
+      <c r="F110" s="2"/>
       <c r="G110" s="4" t="n">
         <v>46262</v>
       </c>
@@ -7090,7 +7083,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7296,7 +7288,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7478,7 +7469,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7558,12 +7548,36 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>EXCEL - PLAN</t>
+          <t>EXCEL - ALLOW EDITING</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EXCEL - PLAN:
+          <t>EXCEL - ALLOW EDITING:
+Add a visible worksheet named exactly .Rules (with the leading dot) as the last tab; if it exists, clear column A and reuse it. Fill column A only, one cell per line below, entering only the text after each "A#: " label. Do not change any other sheet.
+A1: ## SOURCE AND SCOPE
+A2: Preserve Work_Orders, tblWorkOrders, Technicians, current Assigned_To values and source IDs.
+A3: Use the reporting date from Control!B2. State the selected Site, Job_Category, Status and Assigned_To scope beside every report.
+A4: Backlog excludes Closed and Cancelled. Overdue backlog has Due_Date strictly before Control!B2.
+A5: On-time closure rate uses Closed rows only, with Closed_Date &lt;= Due_Date. Display N/A when no Closed rows remain.
+A6: ## FORMATS AND VISUALS
+A7: Display recorded Cost_SGD as S$ with two decimals; keep underlying values exact. Show dates as DD-MMM-YYYY.
+A8: Use white backgrounds, navy titles, blue and teal accents, readable labels and named units; never use colour alone.
+A9: ## DASHBOARD LAYOUT
+A10: Dashboard sheet: title in A1; Site, Job_Category, Status and Assigned_To dropdowns in B2:B5 (All plus source values); the six measures in B7:B12; data-as-at date and selected scope in D2.
+A11: Six KPI tiles in D4:I7, one column per tile: title in row 4, large value in row 5, short definition in row 6 and "Checks: PASS" in row 7.
+A12: Charts in a grid below the tiles: work orders by status and by job category side by side, then a full-width stacked bar by site (overdue backlog, other backlog, Closed, Cancelled).
+A13: Slicers for Site, Job_Category, Status and Assigned_To on the right of the tiles, connected to tblWorkOrders. KPI formulas use SUBTOTAL visibility so slicers and dropdowns both filter every tile and chart.
+A14: Put chart summaries, chart-title formulas and KPI checks on Dashboard_Summaries. Never merge cells. Hide gridlines on Dashboard.
+A15: ## DASHBOARD STYLE
+A16: Tiles: white bold text on solid navy #1F4E79 (totals and rates), blue #2E75B6 (backlog, overdue) or teal #2A9D8F (Closed, cost).
+A17: Every chart title states the finding from a cell formula, e.g. "Changi Workshop has the most overdue backlog (18 of 50)".
+A18: Show data labels on bars; no gridlines; rates as % with one decimal. Each chart total must equal B7.
+A19: ## OUTPUT AND REVIEW
+A20: Use structured table references. Preserve the visible .Rules sheet and unrelated sheets, charts and Prompt_Log.
+A21: Keep current owners separate from unapproved assignment proposals. Missing facts and approvals remain UNKNOWN.
+A22: Ask before replacing named output sheets. Reconcile every count, rate and chart against source rows; do not duplicate outputs on rerun.
+EXCEL - PLAN:
 Review the visible .Rules column A for this Northstar workbook. Identify ambiguous instructions or conflicts with the actual source and Control. Propose concise corrections, keeping one idea per cell. Do not edit the source or invent precedence between rules, preferences and Skills.</t>
         </is>
       </c>
@@ -7641,7 +7655,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7685,12 +7698,82 @@
       </c>
       <c r="B2" s="2">
         <f>ROWS(tblWorkOrders[Work_Order_ID])</f>
-        <v/>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      </c>
+      <c r="C2" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Claim_or_Test</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Observed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source_and_Scope</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>As_At</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Verified_By</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/labs/lab-04-workbook-rules/data/Northstar_Work_Orders.xlsx
+++ b/labs/lab-04-workbook-rules/data/Northstar_Work_Orders.xlsx
@@ -545,12 +545,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Rejoin</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>This input is a deterministic checkpoint, not proof of your Copilot output.</t>
+          <t>Work on a copy saved to your OneDrive folder; keep this supplied workbook unchanged.</t>
         </is>
       </c>
     </row>

--- a/labs/lab-04-workbook-rules/data/Northstar_Work_Orders.xlsx
+++ b/labs/lab-04-workbook-rules/data/Northstar_Work_Orders.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Work on a copy saved to your OneDrive folder; keep this supplied workbook unchanged.</t>
+          <t>Synthetic training data. Work on this file in your lab folder.</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -7530,28 +7530,10 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>EXCEL - CHAT ONLY</t>
+          <t>EXCEL - ALLOW EDITING</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>EXCEL - CHAT ONLY:
-Inspect this Northstar workbook. Identify the source table, fixed reporting date, status vocabulary and current owners. List workbook-specific conventions that belong in .Rules rather than account Personalisation. Do not edit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Step 2</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>EXCEL - ALLOW EDITING</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>EXCEL - ALLOW EDITING:
 Add a visible worksheet named exactly .Rules (with the leading dot) as the last tab; if it exists, clear column A and reuse it. Fill column A only, one cell per line below, entering only the text after each "A#: " label. Do not change any other sheet.
@@ -7576,10 +7558,21 @@
 A19: ## OUTPUT AND REVIEW
 A20: Use structured table references. Preserve the visible .Rules sheet and unrelated sheets, charts and Prompt_Log.
 A21: Keep current owners separate from unapproved assignment proposals. Missing facts and approvals remain UNKNOWN.
-A22: Ask before replacing named output sheets. Reconcile every count, rate and chart against source rows; do not duplicate outputs on rerun.
-EXCEL - PLAN:
-Review the visible .Rules column A for this Northstar workbook. Identify ambiguous instructions or conflicts with the actual source and Control. Propose concise corrections, keeping one idea per cell. Do not edit the source or invent precedence between rules, preferences and Skills.</t>
-        </is>
+A22: Ask before replacing named output sheets. Reconcile every count, rate and chart against source rows; do not duplicate outputs on rerun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Step 2</t>
+        </is>
+      </c>
+      <c r="B3" s="2">
+        <f>"Reporting date</f>
+      </c>
+      <c r="C3" s="2">
+        <f>"Reporting date: "&amp;TEXT(Control!B2,"yyyy-mm-dd")</f>
       </c>
     </row>
     <row r="4">
@@ -7596,7 +7589,7 @@
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>EXCEL - ALLOW EDITING:
-Apply only my reviewed .Rules corrections. Keep the sheet visible, one instruction per column-A cell, and retain the reporting-date formula. Preserve source data, Control and unrelated sheets.</t>
+Add a sheet named Rules_Test with the total work orders, backlog, overdue backlog, on-time closure rate and total cost from tblWorkOrders, using formulas.</t>
         </is>
       </c>
     </row>
@@ -7608,49 +7601,13 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>EXCEL - ALLOW EDITING</t>
+          <t>EXCEL - CHAT ONLY</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EXCEL - ALLOW EDITING:
-Create Rules_Test for Northstar Water Services from tblWorkOrders using the visible workbook .Rules. Include total, backlog, overdue, on-time Closed rate and recorded cost with formula/source evidence. Show date and All scope. Keep source owners and values unchanged.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Step 5</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>EXCEL - CHAT ONLY</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
           <t>EXCEL - CHAT ONLY:
-In this copied Northstar workbook, identify the visible .Rules instructions and reporting-date formula result. Explain which guidance travels with the workbook and which account preferences do not. Verify Rules_Test against Control without changing records.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Step 6</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>EXCEL - CHAT ONLY</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>EXCEL - CHAT ONLY:
-Compare Personalisation, .Rules and a reusable Skill for Northstar reporting. Place currency preferences, this workbook’s backlog/date rules and the repeatable Pareto workflow in the right scope. Identify conflicts requiring clarification and the checks a person still must perform.</t>
+What rules does this workbook give you? List them briefly.</t>
         </is>
       </c>
     </row>

--- a/labs/lab-04-workbook-rules/data/Northstar_Work_Orders.xlsx
+++ b/labs/lab-04-workbook-rules/data/Northstar_Work_Orders.xlsx
@@ -154,9 +154,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblWorkOrders" displayName="tblWorkOrders" ref="A1:M121" headerRowCount="1">
-  <autoFilter ref="A1:M121"/>
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblWorkOrders" displayName="tblWorkOrders" ref="A1:N121" headerRowCount="1">
+  <autoFilter ref="A1:N121"/>
+  <tableColumns count="14">
     <tableColumn id="1" name="Work_Order_ID"/>
     <tableColumn id="2" name="Site"/>
     <tableColumn id="3" name="Job_Category"/>
@@ -170,6 +170,7 @@
     <tableColumn id="11" name="Actual_Hours"/>
     <tableColumn id="12" name="Cost_SGD"/>
     <tableColumn id="13" name="Description"/>
+    <tableColumn id="14" name="Failure_Mode"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -565,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M121"/>
+  <dimension ref="A1:N121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -581,6 +582,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -649,6 +651,11 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Failure_Mode</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -704,6 +711,11 @@
           <t>Leak Repair scheduled or reactive task 001</t>
         </is>
       </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -757,6 +769,11 @@
       <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 002</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -812,6 +829,11 @@
           <t>Leak Repair scheduled or reactive task 003</t>
         </is>
       </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -865,6 +887,11 @@
           <t>Leak Repair scheduled or reactive task 004</t>
         </is>
       </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -918,6 +945,11 @@
           <t>Valve Repair scheduled or reactive task 005</t>
         </is>
       </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -973,6 +1005,11 @@
           <t>Valve Repair scheduled or reactive task 006</t>
         </is>
       </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1026,6 +1063,11 @@
       <c r="M8" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 007</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
         </is>
       </c>
     </row>
@@ -1081,6 +1123,11 @@
           <t>Valve Repair scheduled or reactive task 008</t>
         </is>
       </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1134,6 +1181,11 @@
           <t>Pipe Replacement scheduled or reactive task 009</t>
         </is>
       </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1187,6 +1239,11 @@
           <t>Pipe Replacement scheduled or reactive task 010</t>
         </is>
       </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1242,6 +1299,11 @@
           <t>Pipe Replacement scheduled or reactive task 011</t>
         </is>
       </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1295,6 +1357,11 @@
       <c r="M13" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 012</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -1346,6 +1413,11 @@
           <t>Pump Service scheduled or reactive task 013</t>
         </is>
       </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1399,6 +1471,11 @@
           <t>Pump Service scheduled or reactive task 014</t>
         </is>
       </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1452,6 +1529,11 @@
           <t>Pump Service scheduled or reactive task 015</t>
         </is>
       </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1507,6 +1589,11 @@
           <t>Pump Service scheduled or reactive task 016</t>
         </is>
       </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1560,6 +1647,11 @@
       <c r="M18" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 017</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -1615,6 +1707,11 @@
           <t>Meter Service scheduled or reactive task 018</t>
         </is>
       </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1668,6 +1765,11 @@
           <t>Meter Service scheduled or reactive task 019</t>
         </is>
       </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1721,6 +1823,11 @@
           <t>Meter Service scheduled or reactive task 020</t>
         </is>
       </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Meter fault</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1776,6 +1883,11 @@
           <t>Leak Repair scheduled or reactive task 021</t>
         </is>
       </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1829,6 +1941,11 @@
       <c r="M23" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 022</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -1884,6 +2001,11 @@
           <t>Leak Repair scheduled or reactive task 023</t>
         </is>
       </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1937,6 +2059,11 @@
           <t>Leak Repair scheduled or reactive task 024</t>
         </is>
       </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1986,6 +2113,11 @@
           <t>Valve Repair scheduled or reactive task 025</t>
         </is>
       </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2041,6 +2173,11 @@
           <t>Valve Repair scheduled or reactive task 026</t>
         </is>
       </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2094,6 +2231,11 @@
       <c r="M28" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 027</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
         </is>
       </c>
     </row>
@@ -2149,6 +2291,11 @@
           <t>Valve Repair scheduled or reactive task 028</t>
         </is>
       </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2202,6 +2349,11 @@
           <t>Pipe Replacement scheduled or reactive task 029</t>
         </is>
       </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2255,6 +2407,11 @@
           <t>Pipe Replacement scheduled or reactive task 030</t>
         </is>
       </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2310,6 +2467,11 @@
           <t>Pipe Replacement scheduled or reactive task 031</t>
         </is>
       </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2363,6 +2525,11 @@
       <c r="M33" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 032</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -2418,6 +2585,11 @@
           <t>Pump Service scheduled or reactive task 033</t>
         </is>
       </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2471,6 +2643,11 @@
           <t>Pump Service scheduled or reactive task 034</t>
         </is>
       </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2524,6 +2701,11 @@
           <t>Pump Service scheduled or reactive task 035</t>
         </is>
       </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2579,6 +2761,11 @@
           <t>Pump Service scheduled or reactive task 036</t>
         </is>
       </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2632,6 +2819,11 @@
       <c r="M38" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 037</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -2687,6 +2879,11 @@
           <t>Meter Service scheduled or reactive task 038</t>
         </is>
       </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2740,6 +2937,11 @@
           <t>Meter Service scheduled or reactive task 039</t>
         </is>
       </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Meter fault</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2793,6 +2995,11 @@
           <t>Meter Service scheduled or reactive task 040</t>
         </is>
       </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2848,6 +3055,11 @@
           <t>Leak Repair scheduled or reactive task 041</t>
         </is>
       </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2901,6 +3113,11 @@
       <c r="M43" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 042</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
@@ -2956,6 +3173,11 @@
           <t>Leak Repair scheduled or reactive task 043</t>
         </is>
       </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>Third-party damage</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3009,6 +3231,11 @@
           <t>Leak Repair scheduled or reactive task 044</t>
         </is>
       </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3062,6 +3289,11 @@
           <t>Valve Repair scheduled or reactive task 045</t>
         </is>
       </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3117,6 +3349,11 @@
           <t>Valve Repair scheduled or reactive task 046</t>
         </is>
       </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3170,6 +3407,11 @@
       <c r="M48" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 047</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
         </is>
       </c>
     </row>
@@ -3225,6 +3467,11 @@
           <t>Valve Repair scheduled or reactive task 048</t>
         </is>
       </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3274,6 +3521,11 @@
           <t>Pipe Replacement scheduled or reactive task 049</t>
         </is>
       </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3327,6 +3579,11 @@
           <t>Pipe Replacement scheduled or reactive task 050</t>
         </is>
       </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3382,6 +3639,11 @@
           <t>Pipe Replacement scheduled or reactive task 051</t>
         </is>
       </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3435,6 +3697,11 @@
       <c r="M53" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 052</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -3490,6 +3757,11 @@
           <t>Pump Service scheduled or reactive task 053</t>
         </is>
       </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3543,6 +3815,11 @@
           <t>Pump Service scheduled or reactive task 054</t>
         </is>
       </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3596,6 +3873,11 @@
           <t>Pump Service scheduled or reactive task 055</t>
         </is>
       </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3651,6 +3933,11 @@
           <t>Pump Service scheduled or reactive task 056</t>
         </is>
       </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3704,6 +3991,11 @@
       <c r="M58" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 057</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
@@ -3759,6 +4051,11 @@
           <t>Meter Service scheduled or reactive task 058</t>
         </is>
       </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3812,6 +4109,11 @@
           <t>Meter Service scheduled or reactive task 059</t>
         </is>
       </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>Blockage</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3865,6 +4167,11 @@
           <t>Meter Service scheduled or reactive task 060</t>
         </is>
       </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3920,6 +4227,11 @@
           <t>Leak Repair scheduled or reactive task 061</t>
         </is>
       </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3973,6 +4285,11 @@
       <c r="M63" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 062</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
@@ -4028,6 +4345,11 @@
           <t>Leak Repair scheduled or reactive task 063</t>
         </is>
       </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4081,6 +4403,11 @@
           <t>Leak Repair scheduled or reactive task 064</t>
         </is>
       </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4134,6 +4461,11 @@
           <t>Valve Repair scheduled or reactive task 065</t>
         </is>
       </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4189,6 +4521,11 @@
           <t>Valve Repair scheduled or reactive task 066</t>
         </is>
       </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4242,6 +4579,11 @@
       <c r="M68" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 067</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
         </is>
       </c>
     </row>
@@ -4297,6 +4639,11 @@
           <t>Valve Repair scheduled or reactive task 068</t>
         </is>
       </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4350,6 +4697,11 @@
           <t>Pipe Replacement scheduled or reactive task 069</t>
         </is>
       </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -4403,6 +4755,11 @@
           <t>Pipe Replacement scheduled or reactive task 070</t>
         </is>
       </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4458,6 +4815,11 @@
           <t>Pipe Replacement scheduled or reactive task 071</t>
         </is>
       </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -4511,6 +4873,11 @@
       <c r="M73" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 072</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -4562,6 +4929,11 @@
           <t>Pump Service scheduled or reactive task 073</t>
         </is>
       </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -4615,6 +4987,11 @@
           <t>Pump Service scheduled or reactive task 074</t>
         </is>
       </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4668,6 +5045,11 @@
           <t>Pump Service scheduled or reactive task 075</t>
         </is>
       </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -4723,6 +5105,11 @@
           <t>Pump Service scheduled or reactive task 076</t>
         </is>
       </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4776,6 +5163,11 @@
       <c r="M78" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 077</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
@@ -4831,6 +5223,11 @@
           <t>Meter Service scheduled or reactive task 078</t>
         </is>
       </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Meter fault</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -4884,6 +5281,11 @@
           <t>Meter Service scheduled or reactive task 079</t>
         </is>
       </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -4937,6 +5339,11 @@
           <t>Meter Service scheduled or reactive task 080</t>
         </is>
       </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -4992,6 +5399,11 @@
           <t>Leak Repair scheduled or reactive task 081</t>
         </is>
       </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -5045,6 +5457,11 @@
       <c r="M83" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 082</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>Third-party damage</t>
         </is>
       </c>
     </row>
@@ -5100,6 +5517,11 @@
           <t>Leak Repair scheduled or reactive task 083</t>
         </is>
       </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5153,6 +5575,11 @@
           <t>Leak Repair scheduled or reactive task 084</t>
         </is>
       </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5202,6 +5629,11 @@
           <t>Valve Repair scheduled or reactive task 085</t>
         </is>
       </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -5257,6 +5689,11 @@
           <t>Valve Repair scheduled or reactive task 086</t>
         </is>
       </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -5310,6 +5747,11 @@
       <c r="M88" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 087</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
         </is>
       </c>
     </row>
@@ -5365,6 +5807,11 @@
           <t>Valve Repair scheduled or reactive task 088</t>
         </is>
       </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -5418,6 +5865,11 @@
           <t>Pipe Replacement scheduled or reactive task 089</t>
         </is>
       </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -5471,6 +5923,11 @@
           <t>Pipe Replacement scheduled or reactive task 090</t>
         </is>
       </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -5526,6 +5983,11 @@
           <t>Pipe Replacement scheduled or reactive task 091</t>
         </is>
       </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -5579,6 +6041,11 @@
       <c r="M93" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 092</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -5634,6 +6101,11 @@
           <t>Pump Service scheduled or reactive task 093</t>
         </is>
       </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -5687,6 +6159,11 @@
           <t>Pump Service scheduled or reactive task 094</t>
         </is>
       </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -5740,6 +6217,11 @@
           <t>Pump Service scheduled or reactive task 095</t>
         </is>
       </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -5795,6 +6277,11 @@
           <t>Pump Service scheduled or reactive task 096</t>
         </is>
       </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -5848,6 +6335,11 @@
       <c r="M98" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 097</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
@@ -5903,6 +6395,11 @@
           <t>Meter Service scheduled or reactive task 098</t>
         </is>
       </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Blockage</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -5956,6 +6453,11 @@
           <t>Meter Service scheduled or reactive task 099</t>
         </is>
       </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -6009,6 +6511,11 @@
           <t>Meter Service scheduled or reactive task 100</t>
         </is>
       </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -6064,6 +6571,11 @@
           <t>Leak Repair scheduled or reactive task 101</t>
         </is>
       </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -6117,6 +6629,11 @@
       <c r="M103" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 102</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -6172,6 +6689,11 @@
           <t>Leak Repair scheduled or reactive task 103</t>
         </is>
       </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -6225,6 +6747,11 @@
           <t>Leak Repair scheduled or reactive task 104</t>
         </is>
       </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -6278,6 +6805,11 @@
           <t>Valve Repair scheduled or reactive task 105</t>
         </is>
       </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -6333,6 +6865,11 @@
           <t>Valve Repair scheduled or reactive task 106</t>
         </is>
       </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -6386,6 +6923,11 @@
       <c r="M108" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 107</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
         </is>
       </c>
     </row>
@@ -6441,6 +6983,11 @@
           <t>Valve Repair scheduled or reactive task 108</t>
         </is>
       </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -6490,6 +7037,11 @@
           <t>Pipe Replacement scheduled or reactive task 109</t>
         </is>
       </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -6543,6 +7095,11 @@
           <t>Pipe Replacement scheduled or reactive task 110</t>
         </is>
       </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -6598,6 +7155,11 @@
           <t>Pipe Replacement scheduled or reactive task 111</t>
         </is>
       </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -6651,6 +7213,11 @@
       <c r="M113" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 112</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -6706,6 +7273,11 @@
           <t>Pump Service scheduled or reactive task 113</t>
         </is>
       </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -6759,6 +7331,11 @@
           <t>Pump Service scheduled or reactive task 114</t>
         </is>
       </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -6812,6 +7389,11 @@
           <t>Pump Service scheduled or reactive task 115</t>
         </is>
       </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -6867,6 +7449,11 @@
           <t>Pump Service scheduled or reactive task 116</t>
         </is>
       </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -6920,6 +7507,11 @@
       <c r="M118" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 117</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Meter fault</t>
         </is>
       </c>
     </row>
@@ -6975,6 +7567,11 @@
           <t>Meter Service scheduled or reactive task 118</t>
         </is>
       </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -7028,6 +7625,11 @@
           <t>Meter Service scheduled or reactive task 119</t>
         </is>
       </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -7079,6 +7681,11 @@
       <c r="M121" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 120</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
